--- a/data/market-sweeps/Poland.xlsx
+++ b/data/market-sweeps/Poland.xlsx
@@ -101,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -117,6 +117,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -482,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -518,6 +519,11 @@
           <t>exchange</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>isin</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -545,6 +551,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -572,6 +579,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -599,6 +607,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -626,6 +635,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -653,6 +663,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -680,6 +691,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -707,6 +719,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -734,6 +747,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -761,6 +775,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -788,6 +803,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -815,6 +831,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -842,6 +859,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -869,6 +887,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -896,6 +915,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -923,6 +943,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -950,6 +971,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -977,6 +999,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1004,6 +1027,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1031,6 +1055,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1058,6 +1083,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1085,6 +1111,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1112,6 +1139,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1139,6 +1167,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1166,6 +1195,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1193,6 +1223,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1220,6 +1251,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1247,6 +1279,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1274,6 +1307,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1301,6 +1335,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1328,6 +1363,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1355,6 +1391,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1382,6 +1419,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1409,6 +1447,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1436,6 +1475,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1463,6 +1503,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1490,6 +1531,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1517,6 +1559,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1544,6 +1587,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1571,6 +1615,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1598,6 +1643,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1625,6 +1671,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1652,6 +1699,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1679,6 +1727,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1706,6 +1755,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1733,6 +1783,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1760,6 +1811,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1787,6 +1839,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1814,6 +1867,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1841,6 +1895,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1868,6 +1923,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1895,6 +1951,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1922,6 +1979,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1949,6 +2007,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1976,6 +2035,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2003,6 +2063,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -2030,6 +2091,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2057,6 +2119,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -2084,6 +2147,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2111,6 +2175,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -2138,6 +2203,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2165,6 +2231,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -2192,6 +2259,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2219,6 +2287,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -2246,6 +2315,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2273,6 +2343,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -2300,6 +2371,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2327,6 +2399,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2354,6 +2427,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2381,6 +2455,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2408,6 +2483,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2435,6 +2511,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2462,6 +2539,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2489,6 +2567,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2516,6 +2595,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2543,6 +2623,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2570,6 +2651,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2597,6 +2679,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2624,6 +2707,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2651,6 +2735,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2678,6 +2763,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2705,6 +2791,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2732,6 +2819,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2759,6 +2847,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2786,6 +2875,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2813,6 +2903,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2840,6 +2931,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2867,6 +2959,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2894,6 +2987,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2921,6 +3015,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2948,6 +3043,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2975,6 +3071,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -3002,6 +3099,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3029,6 +3127,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -3056,6 +3155,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3083,6 +3183,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -3110,6 +3211,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3137,6 +3239,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -3164,6 +3267,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3191,6 +3295,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -3218,6 +3323,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3245,6 +3351,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -3272,6 +3379,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3299,6 +3407,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -3326,6 +3435,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3353,6 +3463,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -3380,6 +3491,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3407,6 +3519,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -3434,6 +3547,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3461,6 +3575,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -3488,6 +3603,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3515,6 +3631,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -3542,6 +3659,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3569,6 +3687,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -3596,6 +3715,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3623,6 +3743,7 @@
           <t>GPW Warsaw</t>
         </is>
       </c>
+      <c r="F116" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E116"/>
